--- a/data/trans_orig/P2B_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158750</t>
+          <t>155303</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>203785</t>
+          <t>205152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>284297</t>
+          <t>283365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>344884</t>
+          <t>346171</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>456301</t>
+          <t>457973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>534548</t>
+          <t>534578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>682272</t>
+          <t>680905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>727307</t>
+          <t>730754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>859855</t>
+          <t>858568</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>920442</t>
+          <t>921374</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1556248</t>
+          <t>1556218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1634495</t>
+          <t>1632823</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,1%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>233963</t>
+          <t>235817</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>290111</t>
+          <t>293239</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>299011</t>
+          <t>302366</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>363937</t>
+          <t>363813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>554939</t>
+          <t>556897</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>640226</t>
+          <t>642110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>905076</t>
+          <t>901948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>961224</t>
+          <t>959370</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>926167</t>
+          <t>926291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>991093</t>
+          <t>987738</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1845065</t>
+          <t>1843181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1930352</t>
+          <t>1928394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76926</t>
+          <t>78030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112739</t>
+          <t>113610</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90122</t>
+          <t>87048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123549</t>
+          <t>121123</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173827</t>
+          <t>177582</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225978</t>
+          <t>226264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270500</t>
+          <t>269629</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306313</t>
+          <t>305209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>255061</t>
+          <t>257487</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288488</t>
+          <t>291562</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>535870</t>
+          <t>535584</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>588021</t>
+          <t>584266</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>498707</t>
+          <t>498664</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>579750</t>
+          <t>585848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>710346</t>
+          <t>705160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>800129</t>
+          <t>801015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1229084</t>
+          <t>1231143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1358587</t>
+          <t>1358193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1884733</t>
+          <t>1878635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1965776</t>
+          <t>1965819</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2073324</t>
+          <t>2072438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2163107</t>
+          <t>2168293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3979349</t>
+          <t>3979743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4108852</t>
+          <t>4106793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>383702</t>
+          <t>380475</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>446002</t>
+          <t>441948</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>544922</t>
+          <t>546455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>617196</t>
+          <t>621909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>950065</t>
+          <t>948230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1041640</t>
+          <t>1042781</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424517</t>
+          <t>428571</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486817</t>
+          <t>490044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>647883</t>
+          <t>643170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>720157</t>
+          <t>718624</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1093958</t>
+          <t>1092817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1185533</t>
+          <t>1187368</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>786447</t>
+          <t>789896</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>863761</t>
+          <t>864941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>867075</t>
+          <t>867858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>948015</t>
+          <t>947548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1678455</t>
+          <t>1677797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1793305</t>
+          <t>1788782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>651644</t>
+          <t>650464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>728958</t>
+          <t>725509</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558586</t>
+          <t>559053</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>639526</t>
+          <t>638743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1228701</t>
+          <t>1233224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1343551</t>
+          <t>1344209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161171</t>
+          <t>162359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203372</t>
+          <t>203100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186990</t>
+          <t>186818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226297</t>
+          <t>228406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>364313</t>
+          <t>360883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>417714</t>
+          <t>419854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,82%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153981</t>
+          <t>154253</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196182</t>
+          <t>194994</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142494</t>
+          <t>140385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181801</t>
+          <t>181973</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308430</t>
+          <t>306290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>361831</t>
+          <t>365261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1370490</t>
+          <t>1363132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1476420</t>
+          <t>1473735</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1648152</t>
+          <t>1642877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1763189</t>
+          <t>1757351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3037134</t>
+          <t>3043417</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3207429</t>
+          <t>3199530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1266856</t>
+          <t>1269541</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1372786</t>
+          <t>1380144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1377282</t>
+          <t>1383120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1492319</t>
+          <t>1497594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2676319</t>
+          <t>2684218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2846614</t>
+          <t>2840331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225050</t>
+          <t>225489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>273270</t>
+          <t>275082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>348783</t>
+          <t>349635</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>412787</t>
+          <t>412112</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>589604</t>
+          <t>591980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>670382</t>
+          <t>671908</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376416</t>
+          <t>374604</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424636</t>
+          <t>424197</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>517224</t>
+          <t>517899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>581228</t>
+          <t>580376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>909315</t>
+          <t>907789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>990093</t>
+          <t>987717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>585048</t>
+          <t>582557</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>657477</t>
+          <t>659410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>756243</t>
+          <t>755464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>836062</t>
+          <t>838302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1355067</t>
+          <t>1359151</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1467874</t>
+          <t>1473453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>835293</t>
+          <t>833360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>907722</t>
+          <t>910213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>773347</t>
+          <t>771107</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>853166</t>
+          <t>853945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1634305</t>
+          <t>1628726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1747112</t>
+          <t>1743028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,19%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146664</t>
+          <t>145324</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185228</t>
+          <t>185062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>188761</t>
+          <t>189177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>230788</t>
+          <t>229280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>345121</t>
+          <t>345156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>403678</t>
+          <t>401741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159595</t>
+          <t>159761</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>198159</t>
+          <t>199499</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177440</t>
+          <t>178948</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>219467</t>
+          <t>219051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>349374</t>
+          <t>351311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>407931</t>
+          <t>407896</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>984898</t>
+          <t>980867</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1085331</t>
+          <t>1088643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1324914</t>
+          <t>1332601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1438718</t>
+          <t>1439290</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2351052</t>
+          <t>2341347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2492132</t>
+          <t>2495818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1401948</t>
+          <t>1398636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1502381</t>
+          <t>1506412</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1508930</t>
+          <t>1508358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1622734</t>
+          <t>1615047</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2942796</t>
+          <t>2939110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3083876</t>
+          <t>3093581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,92%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99061</t>
+          <t>99991</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131134</t>
+          <t>131157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>231895</t>
+          <t>231944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>270418</t>
+          <t>269213</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>342680</t>
+          <t>343552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>392514</t>
+          <t>393998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>306610</t>
+          <t>306587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>338683</t>
+          <t>337753</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>410834</t>
+          <t>412039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>449357</t>
+          <t>449308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>726482</t>
+          <t>724998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>776316</t>
+          <t>775444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>265586</t>
+          <t>266375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>331064</t>
+          <t>331467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>387367</t>
+          <t>384849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>925413</t>
+          <t>970836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>675499</t>
+          <t>677871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1312519</t>
+          <t>1331358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>982232</t>
+          <t>981829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1047710</t>
+          <t>1046921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>820110</t>
+          <t>774687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1358156</t>
+          <t>1360674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1746301</t>
+          <t>1727462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2383321</t>
+          <t>2380949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68242</t>
+          <t>67776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104655</t>
+          <t>104640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76143</t>
+          <t>75919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104120</t>
+          <t>104376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149934</t>
+          <t>150364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197387</t>
+          <t>195928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310671</t>
+          <t>310686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>347084</t>
+          <t>347550</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>345000</t>
+          <t>344744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>372977</t>
+          <t>373201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>667059</t>
+          <t>668518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>714512</t>
+          <t>714082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>453761</t>
+          <t>454729</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>534708</t>
+          <t>533372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>737180</t>
+          <t>735755</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1405245</t>
+          <t>1382477</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1224059</t>
+          <t>1216908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2042570</t>
+          <t>1930034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1631659</t>
+          <t>1632995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1712606</t>
+          <t>1711638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1470650</t>
+          <t>1493418</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2138715</t>
+          <t>2140140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2999692</t>
+          <t>3112228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3818203</t>
+          <t>3825354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2B_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155303</t>
+          <t>159224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205152</t>
+          <t>205943</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>283365</t>
+          <t>286872</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>346171</t>
+          <t>345821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>457973</t>
+          <t>457524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>534578</t>
+          <t>536849</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>680905</t>
+          <t>680114</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>730754</t>
+          <t>726833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>858568</t>
+          <t>858918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>921374</t>
+          <t>917867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1556218</t>
+          <t>1553947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1632823</t>
+          <t>1633272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>235817</t>
+          <t>233982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>293239</t>
+          <t>290353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>302366</t>
+          <t>302620</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>363813</t>
+          <t>362892</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>556897</t>
+          <t>554164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>642110</t>
+          <t>639706</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>901948</t>
+          <t>904834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>959370</t>
+          <t>961205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>926291</t>
+          <t>927212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>987738</t>
+          <t>987484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1843181</t>
+          <t>1845585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1928394</t>
+          <t>1931127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,7%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78030</t>
+          <t>78247</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113610</t>
+          <t>112003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87048</t>
+          <t>87550</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121123</t>
+          <t>125439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>177582</t>
+          <t>175834</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>226264</t>
+          <t>222291</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269629</t>
+          <t>271236</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305209</t>
+          <t>304992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>257487</t>
+          <t>253171</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291562</t>
+          <t>291060</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>535584</t>
+          <t>539557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>584266</t>
+          <t>586014</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>498664</t>
+          <t>494437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>585848</t>
+          <t>581117</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>705160</t>
+          <t>705373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>801015</t>
+          <t>797847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1231143</t>
+          <t>1230628</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1358193</t>
+          <t>1358434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1878635</t>
+          <t>1883366</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1965819</t>
+          <t>1970046</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2072438</t>
+          <t>2075606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2168293</t>
+          <t>2168080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3979743</t>
+          <t>3979502</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4106793</t>
+          <t>4107308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>380475</t>
+          <t>381636</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>441948</t>
+          <t>442565</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>546455</t>
+          <t>547511</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>621909</t>
+          <t>621142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>948230</t>
+          <t>953906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1042781</t>
+          <t>1044809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>428571</t>
+          <t>427954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490044</t>
+          <t>488883</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>643170</t>
+          <t>643937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>718624</t>
+          <t>717568</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1092817</t>
+          <t>1090789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1187368</t>
+          <t>1181692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>789896</t>
+          <t>783024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>864941</t>
+          <t>862503</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>867858</t>
+          <t>868218</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>947548</t>
+          <t>949655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1677797</t>
+          <t>1674889</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1788782</t>
+          <t>1788257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>650464</t>
+          <t>652902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>725509</t>
+          <t>732381</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>559053</t>
+          <t>556946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>638743</t>
+          <t>638383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1233224</t>
+          <t>1233749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1344209</t>
+          <t>1347117</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>162359</t>
+          <t>162254</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203100</t>
+          <t>203862</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186818</t>
+          <t>186627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>228406</t>
+          <t>227512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>360883</t>
+          <t>358456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>419854</t>
+          <t>417978</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>154253</t>
+          <t>153491</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>194994</t>
+          <t>195099</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140385</t>
+          <t>141279</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181973</t>
+          <t>182164</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>306290</t>
+          <t>308166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>365261</t>
+          <t>367688</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1363132</t>
+          <t>1364802</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1473735</t>
+          <t>1472924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1642877</t>
+          <t>1636717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1757351</t>
+          <t>1753473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3043417</t>
+          <t>3047402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3199530</t>
+          <t>3200227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1269541</t>
+          <t>1270352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1380144</t>
+          <t>1378474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1383120</t>
+          <t>1386998</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1497594</t>
+          <t>1503754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2684218</t>
+          <t>2683521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2840331</t>
+          <t>2836346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225489</t>
+          <t>225941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>275082</t>
+          <t>275404</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>349635</t>
+          <t>345605</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>412112</t>
+          <t>407267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>591980</t>
+          <t>587209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>671908</t>
+          <t>665670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>374604</t>
+          <t>374282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424197</t>
+          <t>423745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>517899</t>
+          <t>522744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>580376</t>
+          <t>584406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>907789</t>
+          <t>914027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>987717</t>
+          <t>992488</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>582557</t>
+          <t>582973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>659410</t>
+          <t>657238</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>755464</t>
+          <t>755355</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>838302</t>
+          <t>835050</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1359151</t>
+          <t>1361332</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1473453</t>
+          <t>1475009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>833360</t>
+          <t>835532</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>910213</t>
+          <t>909797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>771107</t>
+          <t>774359</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>853945</t>
+          <t>854054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1628726</t>
+          <t>1627170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1743028</t>
+          <t>1740847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145324</t>
+          <t>144856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185062</t>
+          <t>184686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>189177</t>
+          <t>186956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>229280</t>
+          <t>229422</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>345156</t>
+          <t>349136</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>401741</t>
+          <t>403827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159761</t>
+          <t>160137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>199499</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178948</t>
+          <t>178806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>219051</t>
+          <t>221272</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>351311</t>
+          <t>349225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>407896</t>
+          <t>403916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>980867</t>
+          <t>987827</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1088643</t>
+          <t>1089182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1332601</t>
+          <t>1324328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1439290</t>
+          <t>1442155</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2341347</t>
+          <t>2342542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2495818</t>
+          <t>2492814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1398636</t>
+          <t>1398097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1506412</t>
+          <t>1499452</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1508358</t>
+          <t>1505493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1615047</t>
+          <t>1623320</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2939110</t>
+          <t>2942114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3093581</t>
+          <t>3092386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>114413</t>
+          <t>125379</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99991</t>
+          <t>108692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131157</t>
+          <t>142648</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>251457</t>
+          <t>278715</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>231944</t>
+          <t>259326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>269213</t>
+          <t>299309</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>365870</t>
+          <t>404094</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>343552</t>
+          <t>377783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>393998</t>
+          <t>430432</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>323331</t>
+          <t>353132</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>306587</t>
+          <t>335863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>337753</t>
+          <t>369819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>429795</t>
+          <t>466580</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>412039</t>
+          <t>445986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>449308</t>
+          <t>485969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>753126</t>
+          <t>819712</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>724998</t>
+          <t>793374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>775444</t>
+          <t>846023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,13%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>437744</t>
+          <t>478511</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>437744</t>
+          <t>478511</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>437744</t>
+          <t>478511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>681252</t>
+          <t>745295</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>681252</t>
+          <t>745295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>681252</t>
+          <t>745295</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1118996</t>
+          <t>1223806</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1118996</t>
+          <t>1223806</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1118996</t>
+          <t>1223806</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>296667</t>
+          <t>348450</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>266375</t>
+          <t>313315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>331467</t>
+          <t>381554</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>562527</t>
+          <t>414441</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>384849</t>
+          <t>382060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>970836</t>
+          <t>449088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>859194</t>
+          <t>762890</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>677871</t>
+          <t>715600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1331358</t>
+          <t>815303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1016629</t>
+          <t>1085660</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>981829</t>
+          <t>1052556</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1046921</t>
+          <t>1120795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1182996</t>
+          <t>1206520</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>774687</t>
+          <t>1171873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1360674</t>
+          <t>1238901</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2199626</t>
+          <t>2292181</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1727462</t>
+          <t>2239768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2380949</t>
+          <t>2339471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1313296</t>
+          <t>1434110</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1313296</t>
+          <t>1434110</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1313296</t>
+          <t>1434110</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1745523</t>
+          <t>1620961</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1745523</t>
+          <t>1620961</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1745523</t>
+          <t>1620961</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3058820</t>
+          <t>3055071</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3058820</t>
+          <t>3055071</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3058820</t>
+          <t>3055071</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>84388</t>
+          <t>96553</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67776</t>
+          <t>77794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104640</t>
+          <t>119362</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89634</t>
+          <t>104012</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75919</t>
+          <t>87361</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104376</t>
+          <t>120187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>174021</t>
+          <t>200565</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150364</t>
+          <t>177033</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195928</t>
+          <t>225292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>330938</t>
+          <t>360380</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310686</t>
+          <t>337571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>347550</t>
+          <t>379139</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>359486</t>
+          <t>403530</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>344744</t>
+          <t>387355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>373201</t>
+          <t>420181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>690425</t>
+          <t>763911</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>668518</t>
+          <t>739184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>714082</t>
+          <t>787443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>415326</t>
+          <t>456933</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415326</t>
+          <t>456933</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415326</t>
+          <t>456933</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>449120</t>
+          <t>507542</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>449120</t>
+          <t>507542</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>449120</t>
+          <t>507542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>864446</t>
+          <t>964476</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>864446</t>
+          <t>964476</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>864446</t>
+          <t>964476</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>495468</t>
+          <t>570382</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>454729</t>
+          <t>532286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>533372</t>
+          <t>617585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>903617</t>
+          <t>797167</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>735755</t>
+          <t>758654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1382477</t>
+          <t>840019</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1399085</t>
+          <t>1367549</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1216908</t>
+          <t>1301943</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1930034</t>
+          <t>1430383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1670899</t>
+          <t>1799172</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1632995</t>
+          <t>1751969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1711638</t>
+          <t>1837268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1972278</t>
+          <t>2076631</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1493418</t>
+          <t>2033779</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2140140</t>
+          <t>2115144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3643177</t>
+          <t>3875803</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3112228</t>
+          <t>3812969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3825354</t>
+          <t>3941409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,17%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2166367</t>
+          <t>2369554</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2166367</t>
+          <t>2369554</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2166367</t>
+          <t>2369554</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2875895</t>
+          <t>2873798</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2875895</t>
+          <t>2873798</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2875895</t>
+          <t>2873798</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>5042262</t>
+          <t>5243352</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5042262</t>
+          <t>5243352</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5042262</t>
+          <t>5243352</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P2B_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
